--- a/Document/仕様書.xlsx
+++ b/Document/仕様書.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\惑星ゲーム\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86BC0FF-E36A-4D72-9EB5-3D18CA86F5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9571483F-DB4F-428A-887F-AC3630C06EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{4B43DDBB-EB8D-4824-BF78-2AFFF3A10C82}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4B43DDBB-EB8D-4824-BF78-2AFFF3A10C82}"/>
   </bookViews>
   <sheets>
     <sheet name="ゲーム概要" sheetId="1" r:id="rId1"/>
     <sheet name="コンセプト" sheetId="2" r:id="rId2"/>
     <sheet name="メインゲーム仕様" sheetId="3" r:id="rId3"/>
+    <sheet name="画面仕様" sheetId="4" r:id="rId4"/>
+    <sheet name="シーケンス" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="248">
   <si>
     <t>ゲーム概要</t>
     <rPh sb="3" eb="5">
@@ -1609,6 +1612,1796 @@
     <t>以上</t>
     <rPh sb="0" eb="2">
       <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このシートでは「Planet・Archive」の画面仕様について表記しています</t>
+    <rPh sb="24" eb="28">
+      <t>ガメンシヨウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このシートでは「Planet・Archive」の全体シーケンスについて表記しています</t>
+    <rPh sb="24" eb="26">
+      <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーケンス図</t>
+    <rPh sb="5" eb="6">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これをひたすら繰り返す</t>
+    <rPh sb="7" eb="8">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル仕様</t>
+    <rPh sb="4" eb="6">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な要素は以下の通りです</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景画像</t>
+    <rPh sb="0" eb="4">
+      <t>ハイケイガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルフォント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Click to Start</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景画像について</t>
+    <rPh sb="0" eb="4">
+      <t>ハイケイガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この画像に寄せてもらって構いません</t>
+    <rPh sb="2" eb="4">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あらすぎないドット絵でお願いします</t>
+    <rPh sb="9" eb="10">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>濃い青や星、紫色のような宇宙っぽさがあるとなおいいです</t>
+    <rPh sb="0" eb="1">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ムラサキイロ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルフォントについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像の通り英語の上にカタカナで読み仮名を書いてください</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>エイゴ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガナ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面中央にどっしりおいてください</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンチュウオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの方と相談になりますが、タイトルフォントもドットっぽく作っていただきたいです</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Click to Startについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>点滅させてください</t>
+    <rPh sb="0" eb="2">
+      <t>テンメツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これもデザイナーさんとの相談でフォントをドットっぽくしたいです</t>
+    <rPh sb="12" eb="14">
+      <t>ソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルから少し間をあけておいてください</t>
+    <rPh sb="6" eb="7">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アイダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この画面の状態で左クリックをするとメインゲームに移行します</t>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移行する際は暗転させて明るくなってメインゲームに移行する感じでお願いします</t>
+    <rPh sb="0" eb="2">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>アンテン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインゲーム画面について</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レティクル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星</t>
+    <rPh sb="0" eb="2">
+      <t>ワクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とある星</t>
+    <rPh sb="3" eb="4">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残り時間</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現ウェーブで集めた鉱石量</t>
+    <rPh sb="0" eb="1">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>コウセキリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レティクルについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーがマウスで動かす惑星を攻撃できる範囲を表したもの</t>
+    <rPh sb="10" eb="11">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初の大きさや攻撃までの挙動はメインゲーム仕様を参考にしてください</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今のところは半透明ですが、見やすいものがあったら変更します</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ハントウメイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星について</t>
+    <rPh sb="0" eb="2">
+      <t>ワクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーが壊す対象のもの</t>
+    <rPh sb="6" eb="7">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームが進んでいくと大きさや色が変化します（この画面では三角のもの）</t>
+    <rPh sb="4" eb="5">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕様についてはメインゲーム仕様を参考にしてください</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とある星について</t>
+    <rPh sb="3" eb="4">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム画面の中心となる星です</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これを中心に惑星が出現、回るようにします</t>
+    <rPh sb="3" eb="5">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現段階では真っ黒で大丈夫ですが、全体の色のバランスを見てデザイナーの方に描いていただきたいです</t>
+    <rPh sb="0" eb="3">
+      <t>ゲンダンカイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ダイジョウブ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残り時間について</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウェーブ中の残り時間を記載する場所です</t>
+    <rPh sb="4" eb="5">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残り時間の左隣に砂時計のイラストを置いて、右に数字で残り時間を表記します</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒダリドナリ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>スナドケイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１ウェーブは１２秒でそれ以上は増えないものとします</t>
+    <rPh sb="8" eb="9">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現ウェーブで集めた鉱石について</t>
+    <rPh sb="0" eb="1">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウェーブ中に集めた鉱石量を記載する場所です</t>
+    <rPh sb="4" eb="5">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>コウセキリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鉱石量の右隣に鉱石のイラストを置いて、左に数字で鉱石量を表記します</t>
+    <rPh sb="0" eb="3">
+      <t>コウセキリョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>トナリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウセキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>コウセキリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数字は100000まで表記します（超える可能性はあります、仮置きで！）</t>
+    <rPh sb="0" eb="2">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カリオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大100000</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小0</t>
+    <rPh sb="0" eb="2">
+      <t>サイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一つも獲得していないときは０で大丈夫です！</t>
+    <rPh sb="0" eb="1">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ダイジョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルツリー画面について</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星制作画面について</t>
+    <rPh sb="0" eb="2">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>セイサクガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星名</t>
+    <rPh sb="0" eb="3">
+      <t>ワクセイメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要鉱石数</t>
+    <rPh sb="0" eb="5">
+      <t>ヒツヨウコウセキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バフ効果</t>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢印マーク</t>
+    <rPh sb="0" eb="2">
+      <t>ヤジルシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルツリー画面に移行した際に今持っている鉱石の総量を記載します</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イマモ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウセキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ソウリョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星名の左側に配置し、左側に数字で記載し、右側に鉱石の絵を配置します</t>
+    <rPh sb="0" eb="3">
+      <t>ワクセイメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ミギガワ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウセキ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１つも持っていないときは０と記載します</t>
+    <rPh sb="3" eb="4">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大　1000000</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小　0</t>
+    <rPh sb="0" eb="2">
+      <t>サイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在表示されている太陽系惑星の名前を表記します</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンザイヒョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="14">
+      <t>タイヨウケイワクセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水星から始まり、海王星でおわります</t>
+    <rPh sb="0" eb="2">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>カイオウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この惑星を作るのに必要な星のかけらの数を表記します（間違って鉱石数で画像作りました、ミスですすいません）</t>
+    <rPh sb="2" eb="4">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>コウセキスウ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ガゾウツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星を作るのに必要な星のかけらの数が足りていないときは、赤で数字を表記します</t>
+    <rPh sb="0" eb="2">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な数などは別のシートで記載しますが、最初の惑星は２０でお願いします</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星を作ると得られる効果を記載します</t>
+    <rPh sb="0" eb="2">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な星のかけらの数と同じ枠に記載します</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このバフは永続的にかかるものです</t>
+    <rPh sb="5" eb="8">
+      <t>エイゾクテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内容は別シートに記載しますが、最初のバフ効果は10%の確率で一発で惑星を壊せるようになるとしてください</t>
+    <rPh sb="0" eb="2">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>イッパツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の惑星を見るときクリックすることで次にいけます</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像の惑星のように右に配置してください</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２つ目以降の惑星は左にも矢印をつけてください</t>
+    <rPh sb="2" eb="5">
+      <t>メイコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヤジルシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>真ん中に惑星のイラストを置きます</t>
+    <rPh sb="0" eb="1">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水星なら水星の画像を、金星なら金星の画像を貼ります</t>
+    <rPh sb="0" eb="2">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特にやることはありません</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルツリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル効果</t>
+    <rPh sb="3" eb="5">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次ウェーブへ</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在鉱石量</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウセキリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化していくスキルツリー本体です</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星座モチーフに作っていきます</t>
+    <rPh sb="0" eb="2">
+      <t>セイザ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル内容は別シートで記載します</t>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>枠の中に効果を記載していきます</t>
+    <rPh sb="0" eb="1">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの方と相談しながら作っていきます</t>
+    <rPh sb="6" eb="7">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルツリー画面からメインゲーム画面へ移行するボタンです</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリックで画面が移行します</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惑星製作へ</t>
+    <rPh sb="0" eb="2">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太陽系惑星を製作する画面へ移行します</t>
+    <rPh sb="0" eb="5">
+      <t>タイヨウケイワクセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これもクリックで移行します</t>
+    <rPh sb="8" eb="10">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在鉱石量</t>
+    <rPh sb="0" eb="5">
+      <t>ゲンザイコウセキリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今持っている鉱石量を記載します</t>
+    <rPh sb="0" eb="2">
+      <t>イマモ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>コウセキリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在所有星のかけら数</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンザイショユウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大　100000</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要星のかけら数</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルツリーへ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のウェーブへ</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドラッグでカメラ移動ができます</t>
+    <rPh sb="8" eb="10">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この画像のように中央下に配置してください</t>
+    <rPh sb="2" eb="4">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>チュウオウシタ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１つも持っていないときは０で表記してください</t>
+    <rPh sb="3" eb="4">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在所有星のかけら数</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショユウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルツリー画面と行き来することができるボタンです</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>イキキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>枠の中に文字を置いてください</t>
+    <rPh sb="0" eb="1">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリックで移行します</t>
+    <rPh sb="5" eb="7">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームを開始させることができます</t>
+    <rPh sb="4" eb="6">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これもクリックで行います</t>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他概要</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あくまで配置やこうしたいというものなのでこうしたほうが…など</t>
+    <rPh sb="4" eb="6">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意見はどんどん言ってください！</t>
+    <rPh sb="0" eb="2">
+      <t>イケン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また、枠やおいている図形（青や灰色など）は仮置きなので</t>
+    <rPh sb="3" eb="4">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ズケイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハイイロ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カリオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの方と相談の上変更もあると思います</t>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色関連は私自身見え方が変なので、決めきれない部分や</t>
+    <rPh sb="0" eb="3">
+      <t>イロカンレン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ワタシジシン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変なところも出てくると思いますがよろしくお願いします</t>
+    <rPh sb="0" eb="1">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルト画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数字は小数点第一位まで表記します</t>
+    <rPh sb="0" eb="2">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ショウスウテン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大12:0</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小00:0</t>
+    <rPh sb="0" eb="2">
+      <t>サイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TIME UP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破壊した惑星の数</t>
+    <rPh sb="0" eb="2">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>獲得鉱石量</t>
+    <rPh sb="0" eb="5">
+      <t>カクトクコウセキリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星のかけら獲得量</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カクトクリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイマー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインゲームで使用したタイマーをそのまま使います</t>
+    <rPh sb="7" eb="9">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残り０秒の状態で表記し、数字のところを赤色にしてください</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>枠の中にTIME UPと表記してください</t>
+    <rPh sb="0" eb="1">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのほかにやることは特にないです</t>
+    <rPh sb="10" eb="11">
+      <t>トク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウェーブ中に破壊した惑星の合計を記載します</t>
+    <rPh sb="4" eb="5">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ワクセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのまま書いてもらってOKです</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウェーブ中に獲得した鉱石の量を記載します</t>
+    <rPh sb="4" eb="5">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウセキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これもそのまま書いてください</t>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星のかけら獲得量</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウェーブ中に獲得した星のかけらの量を記載します</t>
+    <rPh sb="4" eb="5">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下同文です</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルツリー画面に移行します</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリックでスキルツリー画面に移行します</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインゲーム画面に移行します</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリックでメインゲーム画面に移行します</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景について</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TIMEUPした状態の画面を、薄く背景として残します</t>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウス</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（背景の注意書きあり）</t>
+    <rPh sb="1" eb="3">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>チュウイガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1617,7 +3410,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1633,8 +3426,32 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1653,6 +3470,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1668,7 +3497,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1676,6 +3505,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -2377,6 +4218,3310 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28014</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>21011</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>56028</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76526</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92A544EB-DA06-40A2-84F5-EE9B7336762B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="1576"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2066084" y="945496"/>
+          <a:ext cx="5574926" cy="3137133"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>140074</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>22355</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>82362</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>21505</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34A3D6F7-BB5F-47C5-9DF4-BCA3391D13E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="1622"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1841967" y="9113127"/>
+          <a:ext cx="5153024" cy="2926687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>295</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>296</xdr:row>
+      <xdr:rowOff>151279</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAD3D7CE-B214-D07A-B345-C091C57DF47D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3710940" y="28346400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0671F3EE-6DD2-D0CD-4F68-E57AED7FF30B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3375660" y="20726400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>16809</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>146761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>119204</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>28014</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{146EBBFC-C353-9A49-3EE3-EA8FB771C674}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1882588" y="19813085"/>
+          <a:ext cx="3296072" cy="2453003"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>168087</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>58954</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>68289</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>112058</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{791506D2-ED8B-B309-24D7-50BC8535E17E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5395631" y="19876557"/>
+          <a:ext cx="4102408" cy="2322295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>168088</xdr:colOff>
+      <xdr:row>271</xdr:row>
+      <xdr:rowOff>134484</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>16870</xdr:colOff>
+      <xdr:row>286</xdr:row>
+      <xdr:rowOff>57013</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51B19F11-A7C9-48F0-4178-ADDB5492146E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1865779" y="29633969"/>
+          <a:ext cx="3882900" cy="2191720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>162484</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>12793</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>38687</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04292344-1214-74A6-5489-91862E805F3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1692087" y="19830396"/>
+          <a:ext cx="4078409" cy="2290016"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="フローチャート: 処理 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80D4E784-2502-AE99-B756-8759F7E23606}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3261360" y="922020"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="フローチャート: 判断 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{676C53CF-ECA6-6156-BE49-C64F6AE75D47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4556760" y="922020"/>
+          <a:ext cx="929640" cy="594360"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>分岐</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>45721</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="フローチャート: 他ページ結合子 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDFF4FD9-82CC-4C10-856D-332D360A77EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1866900" y="876301"/>
+          <a:ext cx="952500" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartOffpageConnector">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>35157</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>21003</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="フローチャート: 処理 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31D0481A-7BFE-4EF9-8995-5814D575ABC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5935980" y="1036320"/>
+          <a:ext cx="850497" cy="356283"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ボタン</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>129541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>60961</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="フローチャート: 他ページ結合子 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC6E2198-F6A2-4808-9CB4-20B49217BB47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3268980" y="2872741"/>
+          <a:ext cx="952500" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartOffpageConnector">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>起動</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="フローチャート: 処理 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B6152F4-2E2F-4EA5-AF29-32BBF514E62B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3246120" y="3939540"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>タイトル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>60961</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線矢印コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54B0D89E-F5DC-C401-0105-20511ECD3466}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="9" idx="2"/>
+          <a:endCxn id="10" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3745230" y="3566161"/>
+          <a:ext cx="0" cy="373379"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="フローチャート: 判断 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED820A6-0F25-47F3-9B0D-88F4F1CE66A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3215640" y="4815840"/>
+          <a:ext cx="1074420" cy="861060"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>クリック</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>した？</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87B36427-788E-4CAC-BF6C-B00B3FE850B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="10" idx="2"/>
+          <a:endCxn id="15" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3745230" y="4495800"/>
+          <a:ext cx="7620" cy="320040"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="直線矢印コネクタ 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DAE3044-5085-410B-97E7-CDC9CFCA2CEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="15" idx="2"/>
+          <a:endCxn id="33" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3752850" y="5676900"/>
+          <a:ext cx="0" cy="685801"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>45721</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="フローチャート: 他ページ結合子 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A8464C3-B9A8-4133-83D9-C39BEAB0DA02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3276600" y="6362701"/>
+          <a:ext cx="952500" cy="693420"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartOffpageConnector">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400"/>
+            <a:t>ゲーム開始</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="コネクタ: カギ線 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55B3031D-33B1-E6F9-0BB6-A057DDAF1187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4290060" y="5246370"/>
+          <a:ext cx="1120140" cy="1131570"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="フローチャート: 処理 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E2C2F95-8E4D-41C1-A153-4C6F0FD62819}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4937760" y="6393180"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>タイトル</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>固定</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="楕円 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A35854A2-9937-4BA9-3191-31E38844228D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5516880" y="5867400"/>
+          <a:ext cx="259080" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>N</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="楕円 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40C52CE0-ECCD-4E74-8881-103CA13DC9D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3375660" y="5821680"/>
+          <a:ext cx="259080" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>45721</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DECADF06-C6F4-447D-AE97-30E24531A8D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="33" idx="2"/>
+          <a:endCxn id="44" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3745230" y="7056121"/>
+          <a:ext cx="7620" cy="510539"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="フローチャート: 処理 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C506CE3D-8C07-4407-91E2-362EDD88CE96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3246120" y="7566660"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>メイン</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ゲーム（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>12</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>秒）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="54" name="直線矢印コネクタ 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D4DCFD9-2867-4E9C-B8BC-7C31D48756F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="44" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3741420" y="8122920"/>
+          <a:ext cx="3810" cy="518160"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="フローチャート: 判断 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5619467F-FA43-41E1-9065-E15FC00C94A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3208020" y="8641080"/>
+          <a:ext cx="1074420" cy="861060"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>強化する？</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="コネクタ: カギ線 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ACB90EC-20A6-478C-801C-D31D9EFDC982}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="82" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="1564005" y="11778615"/>
+          <a:ext cx="5459730" cy="38100"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 140"/>
+            <a:gd name="adj2" fmla="val 9780000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="直線矢印コネクタ 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D4A98F-C113-4335-9E88-58F7ABFE7E7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="57" idx="2"/>
+          <a:endCxn id="64" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3737610" y="9502140"/>
+          <a:ext cx="7620" cy="731520"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="楕円 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{374EBDB0-F20A-4185-8645-7739C791A3AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4533900" y="8785860"/>
+          <a:ext cx="259080" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>N</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="楕円 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E41BA6FC-5AEB-4125-92F5-E17A0A54E487}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3268980" y="9547860"/>
+          <a:ext cx="259080" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="フローチャート: 処理 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9D01E90-4C2D-42B9-9CAC-B6DCFF9C4B2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3238500" y="10233660"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>スキルツリー</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>惑星作成へ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11430</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="68" name="直線矢印コネクタ 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E956FDD9-2AF3-4A46-AAD3-58D6B8D444C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="64" idx="2"/>
+          <a:endCxn id="70" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3737610" y="10789920"/>
+          <a:ext cx="7620" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="70" name="フローチャート: 判断 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC3FDE06-B21F-4C65-9C33-2CC3AFF2AD02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3208020" y="11361420"/>
+          <a:ext cx="1074420" cy="861060"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>鉱石</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>星のかけら</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>足りる？</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="74" name="直線矢印コネクタ 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47BA4683-FB64-465A-8F06-1E5D26B04986}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3737610" y="12207240"/>
+          <a:ext cx="3810" cy="731520"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="76" name="楕円 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4055F86D-8276-4C95-8048-0D0823D1AA96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3413760" y="12336780"/>
+          <a:ext cx="259080" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="フローチャート: 処理 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BF3279A-B5DA-4E91-80AD-F4A6E4667FDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3307080" y="12954000"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>スキル強化</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>惑星製作</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="78" name="コネクタ: カギ線 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{318B8833-D713-427B-ADBE-6D064B4AC92E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="82" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2912745" y="13127355"/>
+          <a:ext cx="2747010" cy="53340"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -277"/>
+            <a:gd name="adj2" fmla="val 3357143"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="80" name="楕円 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F36CAE11-76FF-4E35-B443-C9CB154661BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4366260" y="11818620"/>
+          <a:ext cx="259080" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>N</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="直線矢印コネクタ 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{687C3A97-32FF-4F73-AC36-9E1619BA15A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3790950" y="13502640"/>
+          <a:ext cx="3810" cy="731520"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="82" name="フローチャート: 処理 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DC62CFA-660E-47AC-BB3F-B0179DC6D426}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3314700" y="14249400"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>次ウェーブへ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>64770</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="91" name="直線矢印コネクタ 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3E94BD2-0EC6-41F4-B438-DBF5E6921E2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3798570" y="14790420"/>
+          <a:ext cx="3810" cy="731520"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="92" name="フローチャート: 判断 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E223744-2C95-44D3-826E-D0AAABEA16D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3284220" y="15514320"/>
+          <a:ext cx="1074420" cy="861060"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>１０ウェーブ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>やった？</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>80010</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="93" name="直線矢印コネクタ 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA5857DB-B901-4D9D-8687-157B66527D0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3813810" y="16360140"/>
+          <a:ext cx="3810" cy="731520"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="94" name="フローチャート: 処理 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62F05F76-B279-4703-88E1-47DC699022E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3368040" y="17099280"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ビックバン</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>発動可能</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="95" name="楕円 94">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B479F93-2125-4ABC-B82E-B2C73CFAF45B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3489960" y="16459200"/>
+          <a:ext cx="259080" cy="274320"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>41910</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="96" name="コネクタ: カギ線 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{265E2D4D-7E95-4AE1-84AD-02087757A4D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="92" idx="3"/>
+          <a:endCxn id="98" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4358640" y="15944850"/>
+          <a:ext cx="1596390" cy="1169670"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="98" name="フローチャート: 処理 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72621243-D360-441B-96E5-6B3F6E728158}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5455920" y="17114520"/>
+          <a:ext cx="998220" cy="556260"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="none" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ビックバン</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>発動不可</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="103" name="コネクタ: カギ線 102">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82BB07AC-E7F0-4314-3BCF-FFD195426160}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="94" idx="2"/>
+          <a:endCxn id="44" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1">
+          <a:off x="-1348740" y="12439650"/>
+          <a:ext cx="9810750" cy="621030"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -2330"/>
+            <a:gd name="adj2" fmla="val 210430"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2866,7 +8011,7 @@
   <dimension ref="A1:AM124"/>
   <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="6.69921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3081,8 +8226,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:26" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="H71" s="3" t="s">
+    <row r="71" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H71" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3277,4 +8422,1951 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B48EB819-3610-4376-B09E-EFFEE78BA417}">
+  <dimension ref="A1:AM367"/>
+  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="6.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="F5" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="8:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="8:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H31" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H32" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H33" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
+      <c r="AB36" s="4"/>
+      <c r="AC36" s="4"/>
+      <c r="AD36" s="4"/>
+      <c r="AE36" s="4"/>
+      <c r="AF36" s="4"/>
+      <c r="AG36" s="4"/>
+      <c r="AH36" s="4"/>
+      <c r="AI36" s="4"/>
+      <c r="AJ36" s="4"/>
+      <c r="AK36" s="4"/>
+      <c r="AL36" s="4"/>
+      <c r="AM36" s="4"/>
+    </row>
+    <row r="38" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F38" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F40" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="4"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
+      <c r="AM42" s="4"/>
+    </row>
+    <row r="44" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F45" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F46" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4"/>
+      <c r="AF49" s="4"/>
+      <c r="AG49" s="4"/>
+      <c r="AH49" s="4"/>
+      <c r="AI49" s="4"/>
+      <c r="AJ49" s="4"/>
+      <c r="AK49" s="4"/>
+      <c r="AL49" s="4"/>
+      <c r="AM49" s="4"/>
+    </row>
+    <row r="51" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F51" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F52" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F53" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F54" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F55" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="58" spans="1:39" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="F58" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G81" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G83" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="84" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G84" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="85" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G85" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="88" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4"/>
+      <c r="S88" s="4"/>
+      <c r="T88" s="4"/>
+      <c r="U88" s="4"/>
+      <c r="V88" s="4"/>
+      <c r="W88" s="4"/>
+      <c r="X88" s="4"/>
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="4"/>
+      <c r="AA88" s="4"/>
+      <c r="AB88" s="4"/>
+      <c r="AC88" s="4"/>
+      <c r="AD88" s="4"/>
+      <c r="AE88" s="4"/>
+      <c r="AF88" s="4"/>
+      <c r="AG88" s="4"/>
+      <c r="AH88" s="4"/>
+      <c r="AI88" s="4"/>
+      <c r="AJ88" s="4"/>
+      <c r="AK88" s="4"/>
+      <c r="AL88" s="4"/>
+      <c r="AM88" s="4"/>
+    </row>
+    <row r="90" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F90" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F91" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="92" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F92" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="95" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+      <c r="S95" s="4"/>
+      <c r="T95" s="4"/>
+      <c r="U95" s="4"/>
+      <c r="V95" s="4"/>
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="4"/>
+      <c r="AB95" s="4"/>
+      <c r="AC95" s="4"/>
+      <c r="AD95" s="4"/>
+      <c r="AE95" s="4"/>
+      <c r="AF95" s="4"/>
+      <c r="AG95" s="4"/>
+      <c r="AH95" s="4"/>
+      <c r="AI95" s="4"/>
+      <c r="AJ95" s="4"/>
+      <c r="AK95" s="4"/>
+      <c r="AL95" s="4"/>
+      <c r="AM95" s="4"/>
+    </row>
+    <row r="97" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F97" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="98" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F98" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="99" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F99" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="102" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
+      <c r="T102" s="4"/>
+      <c r="U102" s="4"/>
+      <c r="V102" s="4"/>
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
+      <c r="AB102" s="4"/>
+      <c r="AC102" s="4"/>
+      <c r="AD102" s="4"/>
+      <c r="AE102" s="4"/>
+      <c r="AF102" s="4"/>
+      <c r="AG102" s="4"/>
+      <c r="AH102" s="4"/>
+      <c r="AI102" s="4"/>
+      <c r="AJ102" s="4"/>
+      <c r="AK102" s="4"/>
+      <c r="AL102" s="4"/>
+      <c r="AM102" s="4"/>
+    </row>
+    <row r="104" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F104" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="105" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F105" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="106" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F106" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="109" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="4"/>
+      <c r="T109" s="4"/>
+      <c r="U109" s="4"/>
+      <c r="V109" s="4"/>
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+      <c r="AA109" s="4"/>
+      <c r="AB109" s="4"/>
+      <c r="AC109" s="4"/>
+      <c r="AD109" s="4"/>
+      <c r="AE109" s="4"/>
+      <c r="AF109" s="4"/>
+      <c r="AG109" s="4"/>
+      <c r="AH109" s="4"/>
+      <c r="AI109" s="4"/>
+      <c r="AJ109" s="4"/>
+      <c r="AK109" s="4"/>
+      <c r="AL109" s="4"/>
+      <c r="AM109" s="4"/>
+    </row>
+    <row r="111" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F111" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="112" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F112" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="113" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F113" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="114" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F114" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="116" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F116" t="s">
+        <v>223</v>
+      </c>
+      <c r="L116" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4"/>
+      <c r="S119" s="4"/>
+      <c r="T119" s="4"/>
+      <c r="U119" s="4"/>
+      <c r="V119" s="4"/>
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
+      <c r="AA119" s="4"/>
+      <c r="AB119" s="4"/>
+      <c r="AC119" s="4"/>
+      <c r="AD119" s="4"/>
+      <c r="AE119" s="4"/>
+      <c r="AF119" s="4"/>
+      <c r="AG119" s="4"/>
+      <c r="AH119" s="4"/>
+      <c r="AI119" s="4"/>
+      <c r="AJ119" s="4"/>
+      <c r="AK119" s="4"/>
+      <c r="AL119" s="4"/>
+      <c r="AM119" s="4"/>
+    </row>
+    <row r="121" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F122" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="123" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F123" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="125" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F125" t="s">
+        <v>154</v>
+      </c>
+      <c r="L125" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="126" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F126" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="127" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F127" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A130" s="7"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="F130" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="148" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F148" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="150" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G150" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="151" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G151" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="152" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G152" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="153" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G153" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="154" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G154" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="155" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G155" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="156" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G156" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="157" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G157" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="159" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+      <c r="I159" s="4"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+      <c r="L159" s="4"/>
+      <c r="M159" s="4"/>
+      <c r="N159" s="4"/>
+      <c r="O159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="4"/>
+      <c r="R159" s="4"/>
+      <c r="S159" s="4"/>
+      <c r="T159" s="4"/>
+      <c r="U159" s="4"/>
+      <c r="V159" s="4"/>
+      <c r="W159" s="4"/>
+      <c r="X159" s="4"/>
+      <c r="Y159" s="4"/>
+      <c r="Z159" s="4"/>
+      <c r="AA159" s="4"/>
+      <c r="AB159" s="4"/>
+      <c r="AC159" s="4"/>
+      <c r="AD159" s="4"/>
+      <c r="AE159" s="4"/>
+      <c r="AF159" s="4"/>
+      <c r="AG159" s="4"/>
+      <c r="AH159" s="4"/>
+      <c r="AI159" s="4"/>
+      <c r="AJ159" s="4"/>
+      <c r="AK159" s="4"/>
+      <c r="AL159" s="4"/>
+      <c r="AM159" s="4"/>
+    </row>
+    <row r="161" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G161" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="162" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G162" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="165" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+      <c r="I165" s="4"/>
+      <c r="J165" s="4"/>
+      <c r="K165" s="4"/>
+      <c r="L165" s="4"/>
+      <c r="M165" s="4"/>
+      <c r="N165" s="4"/>
+      <c r="O165" s="4"/>
+      <c r="P165" s="4"/>
+      <c r="Q165" s="4"/>
+      <c r="R165" s="4"/>
+      <c r="S165" s="4"/>
+      <c r="T165" s="4"/>
+      <c r="U165" s="4"/>
+      <c r="V165" s="4"/>
+      <c r="W165" s="4"/>
+      <c r="X165" s="4"/>
+      <c r="Y165" s="4"/>
+      <c r="Z165" s="4"/>
+      <c r="AA165" s="4"/>
+      <c r="AB165" s="4"/>
+      <c r="AC165" s="4"/>
+      <c r="AD165" s="4"/>
+      <c r="AE165" s="4"/>
+      <c r="AF165" s="4"/>
+      <c r="AG165" s="4"/>
+      <c r="AH165" s="4"/>
+      <c r="AI165" s="4"/>
+      <c r="AJ165" s="4"/>
+      <c r="AK165" s="4"/>
+      <c r="AL165" s="4"/>
+      <c r="AM165" s="4"/>
+    </row>
+    <row r="167" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G167" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="168" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G168" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="171" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="4"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
+      <c r="L171" s="4"/>
+      <c r="M171" s="4"/>
+      <c r="N171" s="4"/>
+      <c r="O171" s="4"/>
+      <c r="P171" s="4"/>
+      <c r="Q171" s="4"/>
+      <c r="R171" s="4"/>
+      <c r="S171" s="4"/>
+      <c r="T171" s="4"/>
+      <c r="U171" s="4"/>
+      <c r="V171" s="4"/>
+      <c r="W171" s="4"/>
+      <c r="X171" s="4"/>
+      <c r="Y171" s="4"/>
+      <c r="Z171" s="4"/>
+      <c r="AA171" s="4"/>
+      <c r="AB171" s="4"/>
+      <c r="AC171" s="4"/>
+      <c r="AD171" s="4"/>
+      <c r="AE171" s="4"/>
+      <c r="AF171" s="4"/>
+      <c r="AG171" s="4"/>
+      <c r="AH171" s="4"/>
+      <c r="AI171" s="4"/>
+      <c r="AJ171" s="4"/>
+      <c r="AK171" s="4"/>
+      <c r="AL171" s="4"/>
+      <c r="AM171" s="4"/>
+    </row>
+    <row r="173" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G173" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="174" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G174" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="177" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G177" s="4"/>
+      <c r="H177" s="4"/>
+      <c r="I177" s="4"/>
+      <c r="J177" s="4"/>
+      <c r="K177" s="4"/>
+      <c r="L177" s="4"/>
+      <c r="M177" s="4"/>
+      <c r="N177" s="4"/>
+      <c r="O177" s="4"/>
+      <c r="P177" s="4"/>
+      <c r="Q177" s="4"/>
+      <c r="R177" s="4"/>
+      <c r="S177" s="4"/>
+      <c r="T177" s="4"/>
+      <c r="U177" s="4"/>
+      <c r="V177" s="4"/>
+      <c r="W177" s="4"/>
+      <c r="X177" s="4"/>
+      <c r="Y177" s="4"/>
+      <c r="Z177" s="4"/>
+      <c r="AA177" s="4"/>
+      <c r="AB177" s="4"/>
+      <c r="AC177" s="4"/>
+      <c r="AD177" s="4"/>
+      <c r="AE177" s="4"/>
+      <c r="AF177" s="4"/>
+      <c r="AG177" s="4"/>
+      <c r="AH177" s="4"/>
+      <c r="AI177" s="4"/>
+      <c r="AJ177" s="4"/>
+      <c r="AK177" s="4"/>
+      <c r="AL177" s="4"/>
+      <c r="AM177" s="4"/>
+    </row>
+    <row r="179" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G179" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="180" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G180" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="183" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G183" s="4"/>
+      <c r="H183" s="4"/>
+      <c r="I183" s="4"/>
+      <c r="J183" s="4"/>
+      <c r="K183" s="4"/>
+      <c r="L183" s="4"/>
+      <c r="M183" s="4"/>
+      <c r="N183" s="4"/>
+      <c r="O183" s="4"/>
+      <c r="P183" s="4"/>
+      <c r="Q183" s="4"/>
+      <c r="R183" s="4"/>
+      <c r="S183" s="4"/>
+      <c r="T183" s="4"/>
+      <c r="U183" s="4"/>
+      <c r="V183" s="4"/>
+      <c r="W183" s="4"/>
+      <c r="X183" s="4"/>
+      <c r="Y183" s="4"/>
+      <c r="Z183" s="4"/>
+      <c r="AA183" s="4"/>
+      <c r="AB183" s="4"/>
+      <c r="AC183" s="4"/>
+      <c r="AD183" s="4"/>
+      <c r="AE183" s="4"/>
+      <c r="AF183" s="4"/>
+      <c r="AG183" s="4"/>
+      <c r="AH183" s="4"/>
+      <c r="AI183" s="4"/>
+      <c r="AJ183" s="4"/>
+      <c r="AK183" s="4"/>
+      <c r="AL183" s="4"/>
+      <c r="AM183" s="4"/>
+    </row>
+    <row r="185" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G185" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="186" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G186" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="189" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+      <c r="L189" s="4"/>
+      <c r="M189" s="4"/>
+      <c r="N189" s="4"/>
+      <c r="O189" s="4"/>
+      <c r="P189" s="4"/>
+      <c r="Q189" s="4"/>
+      <c r="R189" s="4"/>
+      <c r="S189" s="4"/>
+      <c r="T189" s="4"/>
+      <c r="U189" s="4"/>
+      <c r="V189" s="4"/>
+      <c r="W189" s="4"/>
+      <c r="X189" s="4"/>
+      <c r="Y189" s="4"/>
+      <c r="Z189" s="4"/>
+      <c r="AA189" s="4"/>
+      <c r="AB189" s="4"/>
+      <c r="AC189" s="4"/>
+      <c r="AD189" s="4"/>
+      <c r="AE189" s="4"/>
+      <c r="AF189" s="4"/>
+      <c r="AG189" s="4"/>
+      <c r="AH189" s="4"/>
+      <c r="AI189" s="4"/>
+      <c r="AJ189" s="4"/>
+      <c r="AK189" s="4"/>
+      <c r="AL189" s="4"/>
+      <c r="AM189" s="4"/>
+    </row>
+    <row r="191" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G191" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="192" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G192" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="195" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
+      <c r="I195" s="4"/>
+      <c r="J195" s="4"/>
+      <c r="K195" s="4"/>
+      <c r="L195" s="4"/>
+      <c r="M195" s="4"/>
+      <c r="N195" s="4"/>
+      <c r="O195" s="4"/>
+      <c r="P195" s="4"/>
+      <c r="Q195" s="4"/>
+      <c r="R195" s="4"/>
+      <c r="S195" s="4"/>
+      <c r="T195" s="4"/>
+      <c r="U195" s="4"/>
+      <c r="V195" s="4"/>
+      <c r="W195" s="4"/>
+      <c r="X195" s="4"/>
+      <c r="Y195" s="4"/>
+      <c r="Z195" s="4"/>
+      <c r="AA195" s="4"/>
+      <c r="AB195" s="4"/>
+      <c r="AC195" s="4"/>
+      <c r="AD195" s="4"/>
+      <c r="AE195" s="4"/>
+      <c r="AF195" s="4"/>
+      <c r="AG195" s="4"/>
+      <c r="AH195" s="4"/>
+      <c r="AI195" s="4"/>
+      <c r="AJ195" s="4"/>
+      <c r="AK195" s="4"/>
+      <c r="AL195" s="4"/>
+      <c r="AM195" s="4"/>
+    </row>
+    <row r="197" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G197" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="198" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G198" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="201" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G201" s="4"/>
+      <c r="H201" s="4"/>
+      <c r="I201" s="4"/>
+      <c r="J201" s="4"/>
+      <c r="K201" s="4"/>
+      <c r="L201" s="4"/>
+      <c r="M201" s="4"/>
+      <c r="N201" s="4"/>
+      <c r="O201" s="4"/>
+      <c r="P201" s="4"/>
+      <c r="Q201" s="4"/>
+      <c r="R201" s="4"/>
+      <c r="S201" s="4"/>
+      <c r="T201" s="4"/>
+      <c r="U201" s="4"/>
+      <c r="V201" s="4"/>
+      <c r="W201" s="4"/>
+      <c r="X201" s="4"/>
+      <c r="Y201" s="4"/>
+      <c r="Z201" s="4"/>
+      <c r="AA201" s="4"/>
+      <c r="AB201" s="4"/>
+      <c r="AC201" s="4"/>
+      <c r="AD201" s="4"/>
+      <c r="AE201" s="4"/>
+      <c r="AF201" s="4"/>
+      <c r="AG201" s="4"/>
+      <c r="AH201" s="4"/>
+      <c r="AI201" s="4"/>
+      <c r="AJ201" s="4"/>
+      <c r="AK201" s="4"/>
+      <c r="AL201" s="4"/>
+      <c r="AM201" s="4"/>
+    </row>
+    <row r="203" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G203" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="206" spans="1:39" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A206"/>
+      <c r="B206"/>
+      <c r="C206"/>
+      <c r="F206" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="226" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G226" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="228" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G228" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="229" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G229" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="230" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G230" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="231" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G231" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="234" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D234" s="4"/>
+      <c r="E234" s="4"/>
+      <c r="F234" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G234" s="4"/>
+      <c r="H234" s="4"/>
+      <c r="I234" s="4"/>
+      <c r="J234" s="4"/>
+      <c r="K234" s="4"/>
+      <c r="L234" s="4"/>
+      <c r="M234" s="4"/>
+      <c r="N234" s="4"/>
+      <c r="O234" s="4"/>
+      <c r="P234" s="4"/>
+      <c r="Q234" s="4"/>
+      <c r="R234" s="4"/>
+      <c r="S234" s="4"/>
+      <c r="T234" s="4"/>
+      <c r="U234" s="4"/>
+      <c r="V234" s="4"/>
+      <c r="W234" s="4"/>
+      <c r="X234" s="4"/>
+      <c r="Y234" s="4"/>
+      <c r="Z234" s="4"/>
+      <c r="AA234" s="4"/>
+      <c r="AB234" s="4"/>
+      <c r="AC234" s="4"/>
+      <c r="AD234" s="4"/>
+      <c r="AE234" s="4"/>
+      <c r="AF234" s="4"/>
+      <c r="AG234" s="4"/>
+      <c r="AH234" s="4"/>
+      <c r="AI234" s="4"/>
+      <c r="AJ234" s="4"/>
+      <c r="AK234" s="4"/>
+      <c r="AL234" s="4"/>
+      <c r="AM234" s="4"/>
+    </row>
+    <row r="236" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G236" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="237" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G237" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="238" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G238" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="239" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G239" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="242" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D242" s="4"/>
+      <c r="E242" s="4"/>
+      <c r="F242" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G242" s="4"/>
+      <c r="H242" s="4"/>
+      <c r="I242" s="4"/>
+      <c r="J242" s="4"/>
+      <c r="K242" s="4"/>
+      <c r="L242" s="4"/>
+      <c r="M242" s="4"/>
+      <c r="N242" s="4"/>
+      <c r="O242" s="4"/>
+      <c r="P242" s="4"/>
+      <c r="Q242" s="4"/>
+      <c r="R242" s="4"/>
+      <c r="S242" s="4"/>
+      <c r="T242" s="4"/>
+      <c r="U242" s="4"/>
+      <c r="V242" s="4"/>
+      <c r="W242" s="4"/>
+      <c r="X242" s="4"/>
+      <c r="Y242" s="4"/>
+      <c r="Z242" s="4"/>
+      <c r="AA242" s="4"/>
+      <c r="AB242" s="4"/>
+      <c r="AC242" s="4"/>
+      <c r="AD242" s="4"/>
+      <c r="AE242" s="4"/>
+      <c r="AF242" s="4"/>
+      <c r="AG242" s="4"/>
+      <c r="AH242" s="4"/>
+      <c r="AI242" s="4"/>
+      <c r="AJ242" s="4"/>
+      <c r="AK242" s="4"/>
+      <c r="AL242" s="4"/>
+      <c r="AM242" s="4"/>
+    </row>
+    <row r="244" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G244" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="245" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G245" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="248" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D248" s="4"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G248" s="4"/>
+      <c r="H248" s="4"/>
+      <c r="I248" s="4"/>
+      <c r="J248" s="4"/>
+      <c r="K248" s="4"/>
+      <c r="L248" s="4"/>
+      <c r="M248" s="4"/>
+      <c r="N248" s="4"/>
+      <c r="O248" s="4"/>
+      <c r="P248" s="4"/>
+      <c r="Q248" s="4"/>
+      <c r="R248" s="4"/>
+      <c r="S248" s="4"/>
+      <c r="T248" s="4"/>
+      <c r="U248" s="4"/>
+      <c r="V248" s="4"/>
+      <c r="W248" s="4"/>
+      <c r="X248" s="4"/>
+      <c r="Y248" s="4"/>
+      <c r="Z248" s="4"/>
+      <c r="AA248" s="4"/>
+      <c r="AB248" s="4"/>
+      <c r="AC248" s="4"/>
+      <c r="AD248" s="4"/>
+      <c r="AE248" s="4"/>
+      <c r="AF248" s="4"/>
+      <c r="AG248" s="4"/>
+      <c r="AH248" s="4"/>
+      <c r="AI248" s="4"/>
+      <c r="AJ248" s="4"/>
+      <c r="AK248" s="4"/>
+      <c r="AL248" s="4"/>
+      <c r="AM248" s="4"/>
+    </row>
+    <row r="250" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G250" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="251" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G251" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="254" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D254" s="4"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G254" s="4"/>
+      <c r="H254" s="4"/>
+      <c r="I254" s="4"/>
+      <c r="J254" s="4"/>
+      <c r="K254" s="4"/>
+      <c r="L254" s="4"/>
+      <c r="M254" s="4"/>
+      <c r="N254" s="4"/>
+      <c r="O254" s="4"/>
+      <c r="P254" s="4"/>
+      <c r="Q254" s="4"/>
+      <c r="R254" s="4"/>
+      <c r="S254" s="4"/>
+      <c r="T254" s="4"/>
+      <c r="U254" s="4"/>
+      <c r="V254" s="4"/>
+      <c r="W254" s="4"/>
+      <c r="X254" s="4"/>
+      <c r="Y254" s="4"/>
+      <c r="Z254" s="4"/>
+      <c r="AA254" s="4"/>
+      <c r="AB254" s="4"/>
+      <c r="AC254" s="4"/>
+      <c r="AD254" s="4"/>
+      <c r="AE254" s="4"/>
+      <c r="AF254" s="4"/>
+      <c r="AG254" s="4"/>
+      <c r="AH254" s="4"/>
+      <c r="AI254" s="4"/>
+      <c r="AJ254" s="4"/>
+      <c r="AK254" s="4"/>
+      <c r="AL254" s="4"/>
+      <c r="AM254" s="4"/>
+    </row>
+    <row r="256" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G256" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="257" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G257" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="260" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D260" s="4"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G260" s="4"/>
+      <c r="H260" s="4"/>
+      <c r="I260" s="4"/>
+      <c r="J260" s="4"/>
+      <c r="K260" s="4"/>
+      <c r="L260" s="4"/>
+      <c r="M260" s="4"/>
+      <c r="N260" s="4"/>
+      <c r="O260" s="4"/>
+      <c r="P260" s="4"/>
+      <c r="Q260" s="4"/>
+      <c r="R260" s="4"/>
+      <c r="S260" s="4"/>
+      <c r="T260" s="4"/>
+      <c r="U260" s="4"/>
+      <c r="V260" s="4"/>
+      <c r="W260" s="4"/>
+      <c r="X260" s="4"/>
+      <c r="Y260" s="4"/>
+      <c r="Z260" s="4"/>
+      <c r="AA260" s="4"/>
+      <c r="AB260" s="4"/>
+      <c r="AC260" s="4"/>
+      <c r="AD260" s="4"/>
+      <c r="AE260" s="4"/>
+      <c r="AF260" s="4"/>
+      <c r="AG260" s="4"/>
+      <c r="AH260" s="4"/>
+      <c r="AI260" s="4"/>
+      <c r="AJ260" s="4"/>
+      <c r="AK260" s="4"/>
+      <c r="AL260" s="4"/>
+      <c r="AM260" s="4"/>
+    </row>
+    <row r="262" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G262" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="263" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G263" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="264" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G264" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="267" spans="1:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G267" t="s">
+        <v>167</v>
+      </c>
+      <c r="O267" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="271" spans="1:39" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A271"/>
+      <c r="B271"/>
+      <c r="C271"/>
+      <c r="F271" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="288" spans="7:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G288" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="290" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G290" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="R290" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="291" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G291" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="R291" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="292" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G292" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="293" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G293" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="294" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G294" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="295" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G295" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="299" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D299" s="4"/>
+      <c r="E299" s="4"/>
+      <c r="F299" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G299" s="4"/>
+      <c r="H299" s="4"/>
+      <c r="I299" s="4"/>
+      <c r="J299" s="4"/>
+      <c r="K299" s="4"/>
+      <c r="L299" s="4"/>
+      <c r="M299" s="4"/>
+      <c r="N299" s="4"/>
+      <c r="O299" s="4"/>
+      <c r="P299" s="4"/>
+      <c r="Q299" s="4"/>
+      <c r="R299" s="4"/>
+      <c r="S299" s="4"/>
+      <c r="T299" s="4"/>
+      <c r="U299" s="4"/>
+      <c r="V299" s="4"/>
+      <c r="W299" s="4"/>
+      <c r="X299" s="4"/>
+      <c r="Y299" s="4"/>
+      <c r="Z299" s="4"/>
+      <c r="AA299" s="4"/>
+      <c r="AB299" s="4"/>
+      <c r="AC299" s="4"/>
+      <c r="AD299" s="4"/>
+      <c r="AE299" s="4"/>
+      <c r="AF299" s="4"/>
+      <c r="AG299" s="4"/>
+      <c r="AH299" s="4"/>
+      <c r="AI299" s="4"/>
+      <c r="AJ299" s="4"/>
+      <c r="AK299" s="4"/>
+      <c r="AL299" s="4"/>
+      <c r="AM299" s="4"/>
+    </row>
+    <row r="301" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G301" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="302" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G302" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="303" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G303" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="305" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G305" t="s">
+        <v>201</v>
+      </c>
+      <c r="O305" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="308" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D308" s="4"/>
+      <c r="E308" s="4"/>
+      <c r="F308" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G308" s="4"/>
+      <c r="H308" s="4"/>
+      <c r="I308" s="4"/>
+      <c r="J308" s="4"/>
+      <c r="K308" s="4"/>
+      <c r="L308" s="4"/>
+      <c r="M308" s="4"/>
+      <c r="N308" s="4"/>
+      <c r="O308" s="4"/>
+      <c r="P308" s="4"/>
+      <c r="Q308" s="4"/>
+      <c r="R308" s="4"/>
+      <c r="S308" s="4"/>
+      <c r="T308" s="4"/>
+      <c r="U308" s="4"/>
+      <c r="V308" s="4"/>
+      <c r="W308" s="4"/>
+      <c r="X308" s="4"/>
+      <c r="Y308" s="4"/>
+      <c r="Z308" s="4"/>
+      <c r="AA308" s="4"/>
+      <c r="AB308" s="4"/>
+      <c r="AC308" s="4"/>
+      <c r="AD308" s="4"/>
+      <c r="AE308" s="4"/>
+      <c r="AF308" s="4"/>
+      <c r="AG308" s="4"/>
+      <c r="AH308" s="4"/>
+      <c r="AI308" s="4"/>
+      <c r="AJ308" s="4"/>
+      <c r="AK308" s="4"/>
+      <c r="AL308" s="4"/>
+      <c r="AM308" s="4"/>
+    </row>
+    <row r="310" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G310" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="311" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G311" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="314" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D314" s="4"/>
+      <c r="E314" s="4"/>
+      <c r="F314" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G314" s="4"/>
+      <c r="H314" s="4"/>
+      <c r="I314" s="4"/>
+      <c r="J314" s="4"/>
+      <c r="K314" s="4"/>
+      <c r="L314" s="4"/>
+      <c r="M314" s="4"/>
+      <c r="N314" s="4"/>
+      <c r="O314" s="4"/>
+      <c r="P314" s="4"/>
+      <c r="Q314" s="4"/>
+      <c r="R314" s="4"/>
+      <c r="S314" s="4"/>
+      <c r="T314" s="4"/>
+      <c r="U314" s="4"/>
+      <c r="V314" s="4"/>
+      <c r="W314" s="4"/>
+      <c r="X314" s="4"/>
+      <c r="Y314" s="4"/>
+      <c r="Z314" s="4"/>
+      <c r="AA314" s="4"/>
+      <c r="AB314" s="4"/>
+      <c r="AC314" s="4"/>
+      <c r="AD314" s="4"/>
+      <c r="AE314" s="4"/>
+      <c r="AF314" s="4"/>
+      <c r="AG314" s="4"/>
+      <c r="AH314" s="4"/>
+      <c r="AI314" s="4"/>
+      <c r="AJ314" s="4"/>
+      <c r="AK314" s="4"/>
+      <c r="AL314" s="4"/>
+      <c r="AM314" s="4"/>
+    </row>
+    <row r="316" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G316" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="317" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G317" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="318" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G318" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="321" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D321" s="4"/>
+      <c r="E321" s="4"/>
+      <c r="F321" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G321" s="4"/>
+      <c r="H321" s="4"/>
+      <c r="I321" s="4"/>
+      <c r="J321" s="4"/>
+      <c r="K321" s="4"/>
+      <c r="L321" s="4"/>
+      <c r="M321" s="4"/>
+      <c r="N321" s="4"/>
+      <c r="O321" s="4"/>
+      <c r="P321" s="4"/>
+      <c r="Q321" s="4"/>
+      <c r="R321" s="4"/>
+      <c r="S321" s="4"/>
+      <c r="T321" s="4"/>
+      <c r="U321" s="4"/>
+      <c r="V321" s="4"/>
+      <c r="W321" s="4"/>
+      <c r="X321" s="4"/>
+      <c r="Y321" s="4"/>
+      <c r="Z321" s="4"/>
+      <c r="AA321" s="4"/>
+      <c r="AB321" s="4"/>
+      <c r="AC321" s="4"/>
+      <c r="AD321" s="4"/>
+      <c r="AE321" s="4"/>
+      <c r="AF321" s="4"/>
+      <c r="AG321" s="4"/>
+      <c r="AH321" s="4"/>
+      <c r="AI321" s="4"/>
+      <c r="AJ321" s="4"/>
+      <c r="AK321" s="4"/>
+      <c r="AL321" s="4"/>
+      <c r="AM321" s="4"/>
+    </row>
+    <row r="323" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G323" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="324" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G324" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="325" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G325" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="326" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G326" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="329" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D329" s="4"/>
+      <c r="E329" s="4"/>
+      <c r="F329" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G329" s="4"/>
+      <c r="H329" s="4"/>
+      <c r="I329" s="4"/>
+      <c r="J329" s="4"/>
+      <c r="K329" s="4"/>
+      <c r="L329" s="4"/>
+      <c r="M329" s="4"/>
+      <c r="N329" s="4"/>
+      <c r="O329" s="4"/>
+      <c r="P329" s="4"/>
+      <c r="Q329" s="4"/>
+      <c r="R329" s="4"/>
+      <c r="S329" s="4"/>
+      <c r="T329" s="4"/>
+      <c r="U329" s="4"/>
+      <c r="V329" s="4"/>
+      <c r="W329" s="4"/>
+      <c r="X329" s="4"/>
+      <c r="Y329" s="4"/>
+      <c r="Z329" s="4"/>
+      <c r="AA329" s="4"/>
+      <c r="AB329" s="4"/>
+      <c r="AC329" s="4"/>
+      <c r="AD329" s="4"/>
+      <c r="AE329" s="4"/>
+      <c r="AF329" s="4"/>
+      <c r="AG329" s="4"/>
+      <c r="AH329" s="4"/>
+      <c r="AI329" s="4"/>
+      <c r="AJ329" s="4"/>
+      <c r="AK329" s="4"/>
+      <c r="AL329" s="4"/>
+      <c r="AM329" s="4"/>
+    </row>
+    <row r="331" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G331" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="332" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G332" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="333" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G333" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="336" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D336" s="4"/>
+      <c r="E336" s="4"/>
+      <c r="F336" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G336" s="4"/>
+      <c r="H336" s="4"/>
+      <c r="I336" s="4"/>
+      <c r="J336" s="4"/>
+      <c r="K336" s="4"/>
+      <c r="L336" s="4"/>
+      <c r="M336" s="4"/>
+      <c r="N336" s="4"/>
+      <c r="O336" s="4"/>
+      <c r="P336" s="4"/>
+      <c r="Q336" s="4"/>
+      <c r="R336" s="4"/>
+      <c r="S336" s="4"/>
+      <c r="T336" s="4"/>
+      <c r="U336" s="4"/>
+      <c r="V336" s="4"/>
+      <c r="W336" s="4"/>
+      <c r="X336" s="4"/>
+      <c r="Y336" s="4"/>
+      <c r="Z336" s="4"/>
+      <c r="AA336" s="4"/>
+      <c r="AB336" s="4"/>
+      <c r="AC336" s="4"/>
+      <c r="AD336" s="4"/>
+      <c r="AE336" s="4"/>
+      <c r="AF336" s="4"/>
+      <c r="AG336" s="4"/>
+      <c r="AH336" s="4"/>
+      <c r="AI336" s="4"/>
+      <c r="AJ336" s="4"/>
+      <c r="AK336" s="4"/>
+      <c r="AL336" s="4"/>
+      <c r="AM336" s="4"/>
+    </row>
+    <row r="338" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G338" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="339" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G339" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="340" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G340" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="343" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D343" s="4"/>
+      <c r="E343" s="4"/>
+      <c r="F343" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G343" s="4"/>
+      <c r="H343" s="4"/>
+      <c r="I343" s="4"/>
+      <c r="J343" s="4"/>
+      <c r="K343" s="4"/>
+      <c r="L343" s="4"/>
+      <c r="M343" s="4"/>
+      <c r="N343" s="4"/>
+      <c r="O343" s="4"/>
+      <c r="P343" s="4"/>
+      <c r="Q343" s="4"/>
+      <c r="R343" s="4"/>
+      <c r="S343" s="4"/>
+      <c r="T343" s="4"/>
+      <c r="U343" s="4"/>
+      <c r="V343" s="4"/>
+      <c r="W343" s="4"/>
+      <c r="X343" s="4"/>
+      <c r="Y343" s="4"/>
+      <c r="Z343" s="4"/>
+      <c r="AA343" s="4"/>
+      <c r="AB343" s="4"/>
+      <c r="AC343" s="4"/>
+      <c r="AD343" s="4"/>
+      <c r="AE343" s="4"/>
+      <c r="AF343" s="4"/>
+      <c r="AG343" s="4"/>
+      <c r="AH343" s="4"/>
+      <c r="AI343" s="4"/>
+      <c r="AJ343" s="4"/>
+      <c r="AK343" s="4"/>
+      <c r="AL343" s="4"/>
+      <c r="AM343" s="4"/>
+    </row>
+    <row r="345" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G345" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="346" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G346" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="347" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G347" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="350" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D350" s="4"/>
+      <c r="E350" s="4"/>
+      <c r="F350" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G350" s="4"/>
+      <c r="H350" s="4"/>
+      <c r="I350" s="4"/>
+      <c r="J350" s="4"/>
+      <c r="K350" s="4"/>
+      <c r="L350" s="4"/>
+      <c r="M350" s="4"/>
+      <c r="N350" s="4"/>
+      <c r="O350" s="4"/>
+      <c r="P350" s="4"/>
+      <c r="Q350" s="4"/>
+      <c r="R350" s="4"/>
+      <c r="S350" s="4"/>
+      <c r="T350" s="4"/>
+      <c r="U350" s="4"/>
+      <c r="V350" s="4"/>
+      <c r="W350" s="4"/>
+      <c r="X350" s="4"/>
+      <c r="Y350" s="4"/>
+      <c r="Z350" s="4"/>
+      <c r="AA350" s="4"/>
+      <c r="AB350" s="4"/>
+      <c r="AC350" s="4"/>
+      <c r="AD350" s="4"/>
+      <c r="AE350" s="4"/>
+      <c r="AF350" s="4"/>
+      <c r="AG350" s="4"/>
+      <c r="AH350" s="4"/>
+      <c r="AI350" s="4"/>
+      <c r="AJ350" s="4"/>
+      <c r="AK350" s="4"/>
+      <c r="AL350" s="4"/>
+      <c r="AM350" s="4"/>
+    </row>
+    <row r="352" spans="4:39" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G352" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G353" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A356" s="5"/>
+      <c r="B356" s="5"/>
+      <c r="C356" s="5"/>
+      <c r="F356" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G358" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G359" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G361" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G362" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G363" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G364" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F367" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9B52F2-5B07-4145-957D-3A712D624CD3}">
+  <dimension ref="A1:Q124"/>
+  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="6.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="F5" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="121" spans="5:17" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q121" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="124" spans="5:17" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E124" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CEB91E-7C9B-4C0E-950B-599A2D63359E}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="2.19921875" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="6.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>